--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1117 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1513,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1735,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1865,22 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沪A37970D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1881,12 +1913,12 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1944,22 +1976,22 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A37970D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1992,12 +2024,12 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2011,7 +2043,7 @@
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2055,22 +2087,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2103,12 +2135,12 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2122,7 +2154,7 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2158,7 +2190,1355 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66631D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1441,32 +1445,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,17 +1506,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1518,13 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1564,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1585,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1625,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1683,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1696,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1744,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1764,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1874,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1885,32 +1913,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1918,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,33 +1974,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2032,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2029,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,33 +2093,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2218,32 +2262,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2251,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,33 +2323,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2401,7 +2453,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2440,32 +2492,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2473,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2497,17 +2553,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2517,13 +2573,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2734,7 +2794,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2749,7 +2809,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2864,7 +2924,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2985,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2979,7 +3039,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3079,7 +3139,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3094,7 +3154,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3310,13 +3370,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3398,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3377,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3391,7 +3455,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3435,22 +3499,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3483,12 +3547,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3502,7 +3566,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3539,6 +3603,1033 @@
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66631D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,13 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1655,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,12 +1998,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2353,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2381,32 +2385,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2414,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2438,17 +2446,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2458,13 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2583,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2611,32 +2623,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2644,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2668,17 +2684,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2688,13 +2704,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2722,32 +2742,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2755,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2779,17 +2803,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2799,17 +2823,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2837,32 +2861,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2870,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2894,37 +2922,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2952,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2985,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3009,37 +3041,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3154,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3214,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -3215,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,17 +3275,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3259,13 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3365,7 +3405,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3380,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3408,32 +3448,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3441,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3465,17 +3509,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3485,13 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3639,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3663,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3750,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3717,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3860,32 +3908,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3893,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3917,17 +3969,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3937,12 +3989,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4008,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4047,7 +4099,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4119,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4173,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4288,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4393,13 +4445,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4504,17 +4560,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4522,22 +4578,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4570,12 +4626,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4589,47 +4645,729 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>9/18</t>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,13 +1883,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,22 +1997,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,22 +2346,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2480,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2818,22 +2822,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3175,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3309,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3765,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3880,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3918,24 +3922,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3945,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3984,22 +3988,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4027,32 +4031,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4060,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4084,17 +4092,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4104,13 +4112,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4150,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4171,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,37 +4211,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4253,32 +4269,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4286,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,37 +4330,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4503,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4516,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4540,37 +4564,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4622,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4631,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,37 +4683,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4774,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4800,7 +4828,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4828,32 +4856,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4861,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4885,37 +4917,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4943,32 +4975,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4976,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5000,37 +5036,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5127,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5256,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5264,22 +5300,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5317,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5331,43 +5367,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,18 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1893,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3185,7 +3189,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3423,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,18 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3988,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,7 +4115,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4122,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4241,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,22 +4353,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4632,24 +4640,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4659,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4708,12 +4716,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4866,24 +4874,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4893,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4942,7 +4950,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4985,12 +4993,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -5012,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5061,12 +5069,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5094,32 +5102,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5127,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5151,33 +5163,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5336,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5353,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5377,37 +5397,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5507,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5522,7 +5542,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5550,32 +5570,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5583,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5607,37 +5631,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5737,7 +5761,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5752,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5867,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5977,12 +6001,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6067,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6092,7 +6116,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6158,7 +6182,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6207,12 +6231,587 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>1/18</t>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,22 +4940,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5804,32 +5804,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5837,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5861,32 +5865,32 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5919,32 +5923,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5952,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5976,32 +5984,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6034,32 +6042,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6067,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6091,37 +6103,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6221,7 +6233,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6297,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,7 +6424,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,7 +6654,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6691,7 +6703,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6757,7 +6769,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6811,7 +6823,582 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
           <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,17 +3996,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5532,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,17 +5651,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,24 +6052,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6194,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6218,17 +6222,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6238,12 +6242,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6276,32 +6280,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6309,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6333,32 +6341,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6391,32 +6399,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6424,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6448,32 +6460,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6506,32 +6518,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6539,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6563,17 +6579,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6583,17 +6599,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6621,32 +6637,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6654,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6678,17 +6698,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6698,17 +6718,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6823,7 +6843,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6938,7 +6958,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6999,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7163,12 +7183,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7388,17 +7408,358 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>2/18</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7656,22 +7656,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7704,12 +7704,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7748,16 +7748,131 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr"/>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,17 +3418,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,22 +4234,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,22 +4587,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4749,12 +4749,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq22推进至seq34，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4790,10 +4790,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4821,7 +4833,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4901,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,12 +4957,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5020,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,17 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5254,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5537,12 +5549,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5646,17 +5658,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,22 +5773,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,22 +5892,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5999,22 +6011,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,12 +6135,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6198,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,17 +6254,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,24 +6540,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6555,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6604,12 +6616,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6659,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6674,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6713,17 +6725,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6756,32 +6768,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6789,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,37 +6829,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6887,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6904,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6928,37 +6948,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6986,32 +7006,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7019,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7043,37 +7067,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7101,32 +7125,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7134,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7158,17 +7186,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7178,12 +7206,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7249,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7331,32 +7359,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7364,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7388,17 +7420,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7408,17 +7440,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7541,7 +7573,7 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7589,12 +7621,12 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7633,22 +7665,18 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>83.8</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7758,12 +7786,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7799,7 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7819,12 +7847,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7863,18 +7891,942 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>88.4</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2588,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,22 +4115,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,22 +4353,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq24推进至seq37，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5274,10 +5274,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5305,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5385,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,22 +5551,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,22 +5670,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5972,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6026,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,7 +6142,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6145,7 +6157,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6249,7 +6261,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6329,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6368,22 +6380,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,22 +6499,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,22 +6618,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,22 +6737,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7043,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7201,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7216,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7256,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7277,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,37 +7317,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7451,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7478,32 +7494,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7511,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7535,37 +7555,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7665,7 +7685,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7704,32 +7724,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7737,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7761,37 +7785,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7819,32 +7843,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7852,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7876,37 +7904,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8049,32 +8077,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8082,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8106,37 +8138,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8366,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8542,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,7 +8689,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,7 +8804,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,7 +8858,1038 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,17 +3064,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4363,12 +4363,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,22 +4587,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,22 +6023,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,22 +6975,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,22 +7094,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,24 +7734,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7853,24 +7853,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7962,32 +7962,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7995,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,37 +8023,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8087,24 +8091,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8114,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8163,12 +8167,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8268,7 +8272,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8344,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8383,7 +8387,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8398,7 +8402,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8498,7 +8502,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8541,32 +8545,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8574,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8598,32 +8606,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8656,32 +8664,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8689,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8713,37 +8725,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8771,32 +8783,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8804,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8828,37 +8844,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8958,7 +8974,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8973,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9001,32 +9017,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9034,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9058,17 +9078,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9078,12 +9098,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9149,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9203,7 +9223,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9318,7 +9338,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9399,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9490,7 +9510,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9605,7 +9625,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9654,7 +9674,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9720,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9769,7 +9789,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9782,22 +9802,22 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9830,12 +9850,12 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9849,7 +9869,7 @@
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
@@ -9874,22 +9894,942 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>97.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A37970D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
         <is>
           <t>89.0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr">
+      <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,18 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3423,7 +3427,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,22 +4119,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4602,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4716,12 +4720,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,22 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5081,7 +5085,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5151,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5919,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6142,22 +6146,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6271,7 +6275,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6341,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,22 +6622,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6752,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6871,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7104,12 +7108,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7213,22 +7217,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,22 +7336,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7461,7 +7465,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7531,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7685,18 +7689,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7800,22 +7808,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7919,22 +7927,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8636,7 +8644,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8793,19 +8801,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8820,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8869,12 +8877,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8902,32 +8910,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8935,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8959,17 +8971,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8979,17 +8991,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9027,24 +9039,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9054,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9093,7 +9105,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9103,7 +9115,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9136,32 +9148,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9169,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9193,37 +9209,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9251,32 +9267,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9284,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9308,37 +9328,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9366,32 +9386,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9399,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9423,33 +9447,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9477,32 +9505,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9510,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9534,17 +9566,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9554,17 +9586,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9592,32 +9624,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9625,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9649,37 +9685,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9707,32 +9743,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9740,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9764,37 +9804,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9909,7 +9949,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9970,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10024,7 +10064,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10139,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10254,7 +10294,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10355,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10369,7 +10409,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10484,7 +10524,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10585,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10599,7 +10639,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10700,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10704,17 +10744,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10815,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10824,12 +10864,702 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
           <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,22 +8046,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,17 +8170,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8280,17 +8280,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9634,24 +9634,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9753,24 +9753,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9862,32 +9862,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9895,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9919,37 +9923,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9977,32 +9981,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10010,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,17 +10042,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10054,17 +10062,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10207,32 +10215,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10240,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10264,32 +10276,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10355,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10394,7 +10406,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10409,7 +10421,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10482,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10536,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10639,7 +10651,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10712,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10739,7 +10751,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10815,7 +10827,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10869,7 +10881,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10942,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10984,7 +10996,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10992,7 +11004,7 @@
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -11040,12 +11052,12 @@
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11084,22 +11096,22 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11107,22 +11119,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11155,12 +11167,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11174,7 +11186,7 @@
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
@@ -11199,22 +11211,22 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11222,22 +11234,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11270,12 +11282,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11289,7 +11301,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -11314,22 +11326,22 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11337,22 +11349,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11385,12 +11397,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11404,7 +11416,7 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -11429,22 +11441,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11464,7 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -11462,7 +11474,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11500,12 +11512,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11519,47 +11531,737 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:25</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
         <is>
           <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>97.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>112.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8515,17 +8515,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,17 +8991,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10449,32 +10449,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10482,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10506,17 +10510,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10526,17 +10530,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10651,7 +10655,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10679,32 +10683,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10712,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10736,17 +10744,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10756,17 +10764,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10881,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10996,7 +11004,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11172,7 +11180,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11287,7 +11295,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11326,7 +11334,7 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11341,7 +11349,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11517,7 +11525,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11632,7 +11640,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11747,7 +11755,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11801,7 +11809,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11870,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11977,7 +11985,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12092,7 +12100,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12207,7 +12215,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12251,17 +12259,132 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6627,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7694,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7813,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,17 +8872,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9467,17 +9467,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10459,24 +10459,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>118分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10802,32 +10802,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10835,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10859,17 +10863,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10879,17 +10883,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10917,32 +10921,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10950,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10974,17 +10982,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10994,12 +11002,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11065,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11117,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11188,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,7 +11232,7 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
@@ -11234,7 +11242,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11262,32 +11270,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11295,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11319,17 +11331,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11339,17 +11351,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11377,32 +11389,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11410,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11434,17 +11450,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11454,17 +11470,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11492,32 +11508,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11525,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11549,17 +11569,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11569,7 +11589,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11579,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11607,32 +11627,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11640,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11664,17 +11688,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11684,17 +11708,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11779,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11870,7 +11894,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11909,7 +11933,7 @@
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -11924,7 +11948,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11985,7 +12009,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12039,7 +12063,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12124,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12139,7 +12163,7 @@
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
@@ -12215,7 +12239,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12269,7 +12293,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12354,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12374,17 +12398,247 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
-        <is>
-          <t>90.3</t>
-        </is>
-      </c>
-      <c r="AC101" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>112.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6508,17 +6508,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,17 +7932,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8634,17 +8634,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,17 +8991,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,17 +9705,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10764,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11746,32 +11746,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11779,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11803,17 +11807,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11823,17 +11827,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11861,32 +11865,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -11894,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11918,17 +11926,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11938,17 +11946,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11976,32 +11984,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12009,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12033,17 +12045,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12053,17 +12065,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12091,32 +12103,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12124,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12148,17 +12164,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12168,12 +12184,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12206,32 +12222,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12239,7 +12259,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12263,17 +12283,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12283,17 +12303,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12374,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12408,7 +12428,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12489,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12513,17 +12533,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12604,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12628,12 +12648,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">

--- a/data/export/2026-09-24-浦东78路.xlsx
+++ b/data/export/2026-09-24-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11351,17 +11351,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11946,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12341,32 +12341,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12374,7 +12378,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12398,17 +12402,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12418,17 +12422,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12456,32 +12460,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12489,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12513,17 +12521,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12533,17 +12541,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
